--- a/data/trans_orig/IP36_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP36_2023-Estudios-trans_orig.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables originales" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2023" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q40"/>
+  <dimension ref="A1:W44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,12 +524,18 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos según su situación laboral actual en 2023 (Tasa respuesta: 100,0%)</t>
+          <t>Adultos según su situación laboral actual / solo 2023 en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -542,24 +548,30 @@
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
       <c r="K1" s="3" t="n"/>
       <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="M1" s="3" t="n"/>
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="n"/>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="n"/>
+      <c r="S1" s="3" t="n"/>
+      <c r="T1" s="3" t="n"/>
+      <c r="U1" s="3" t="n"/>
+      <c r="V1" s="3" t="n"/>
+      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -576,65 +588,95 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>n (muestra)</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>N (estimada)</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>n (muestra)</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>N (estimada)</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="V2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -658,6 +700,12 @@
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="n"/>
+      <c r="U3" s="2" t="n"/>
+      <c r="V3" s="2" t="n"/>
+      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -670,67 +718,109 @@
           <t>Otros</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0</v>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>918</v>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>5,88%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>918</v>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -738,70 +828,112 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Incapacidad/invalidez permanente</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>1241</v>
+          <t>Voluntariado social</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>8,46%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>2240</v>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>918</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>3480</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3184</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>918</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>2955</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -809,70 +941,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Estudiante</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>941</v>
+          <t>Incapacidad/invalidez permanente</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1241</t>
+        </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>4334</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,04%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>881</v>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>7,93%</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>1822</v>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>6755</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>3480</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>8019</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -880,70 +1054,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Sus labores/Ama de casa</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>18797</v>
+          <t>Estudiante</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>3039</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>18245</v>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,56%</t>
+        </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>881</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="N7" s="2" t="n">
-        <v>37042</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3555</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1822</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4496</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -951,70 +1167,112 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Jubilado (trabajó anteriormente)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>2223</v>
+          <t>Sus labores/Ama de casa/Trabajo doméstico no remunerado</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18797</t>
+        </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>11283</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>26344</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>6265</v>
+          <t>34,38%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>20,64%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>48,18%</t>
+        </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>18245</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>8487</v>
+          <t>12413</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>26019</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>29,43%</t>
+        </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>37042</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>27946</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>48883</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>31,75%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>23,95%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>41,89%</t>
         </is>
       </c>
     </row>
@@ -1022,70 +1280,112 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Busca primer empleo</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>0</v>
+          <t>Jubilado/a (trabajó anteriormente)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2223</t>
+        </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>597</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>6573</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>12,02%</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>6265</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>0</v>
+          <t>2865</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>11606</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>10,1%</t>
+        </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>8487</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>4353</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>14113</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>7,27%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -1093,70 +1393,112 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Está en el paro y ha trabajado antes</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>12039</v>
+          <t>Busca primer empleo</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>9367</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>21406</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1164,70 +1506,112 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Trabaja</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>19437</v>
+          <t>Está en el paro y ha trabajado antes</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>12039</t>
+        </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>5421</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>27483</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>24089</v>
+          <t>22,02%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>9,91%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>50,26%</t>
+        </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>9367</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>43527</v>
+          <t>5448</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>14661</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>15,11%</t>
+        </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>21406</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>13305</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>37129</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>18,35%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>11,4%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>31,82%</t>
         </is>
       </c>
     </row>
@@ -1235,216 +1619,342 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>54678</v>
+          <t>Trabaja</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>19437</t>
+        </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>27044</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>62004</v>
+          <t>35,55%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>22,04%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>49,46%</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>24089</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>152</v>
-      </c>
-      <c r="N12" s="2" t="n">
-        <v>116682</v>
+          <t>16839</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>30672</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>38,85%</t>
+        </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>43527</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>33298</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>54816</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>37,3%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>28,54%</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>46,98%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>4020</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>54678</t>
+        </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>54678</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>54678</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>4186</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>62004</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="N13" s="2" t="n">
-        <v>8206</v>
+          <t>62004</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>62004</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>116682</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>116682</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>116682</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n"/>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Incapacidad/invalidez permanente</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>8534</v>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>983</t>
+        </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>3139</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>11054</v>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>19588</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>983</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>3419</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -1452,70 +1962,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Estudiante</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>17635</v>
+          <t>Voluntariado social</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>6729</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>15631</v>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>33265</v>
+          <t>1517</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>9319</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>7223</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>3696</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>13038</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -1523,70 +2075,112 @@
       <c r="A16" s="1" t="n"/>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Sus labores/Ama de casa</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>103</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>73257</v>
+          <t>Incapacidad/invalidez permanente</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8534</t>
+        </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>4704</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>14457</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>105</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>81674</v>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,14%</t>
+        </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>11054</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>208</v>
-      </c>
-      <c r="N16" s="2" t="n">
-        <v>154931</v>
+          <t>6340</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>19784</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>19588</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>12534</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>28192</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -1594,70 +2188,112 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Jubilado (trabajó anteriormente)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>9315</v>
+          <t>Estudiante</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>17635</t>
+        </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>11335</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>25585</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>4839</v>
+          <t>3,83%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>5,56%</t>
+        </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>15631</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="N17" s="2" t="n">
-        <v>14154</v>
+          <t>9073</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>24650</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>33265</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>23018</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>43584</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -1665,70 +2301,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Busca primer empleo</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>1866</v>
+          <t>Sus labores/Ama de casa/Trabajo doméstico no remunerado</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>73257</t>
+        </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>56531</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>88855</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>1464</v>
+          <t>15,91%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>12,28%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>19,29%</t>
+        </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>105</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>81674</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="N18" s="2" t="n">
-        <v>3331</v>
+          <t>67767</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>97582</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>15,81%</t>
+        </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>154931</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>133251</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>178454</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>15,86%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>13,64%</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -1736,70 +2414,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Está en el paro y ha trabajado antes</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>88282</v>
+          <t>Jubilado/a (trabajó anteriormente)</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>9315</t>
+        </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>15547</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>94</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>76209</v>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3,38%</t>
+        </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>4839</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="n">
-        <v>183</v>
-      </c>
-      <c r="N19" s="2" t="n">
-        <v>164491</v>
+          <t>1878</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>9437</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>14154</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>8795</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>21690</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -1807,70 +2527,112 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Trabaja</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>388</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>257601</v>
+          <t>Busca primer empleo</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1866</t>
+        </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>438</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>408</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>321561</v>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>1464</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="n">
-        <v>796</v>
-      </c>
-      <c r="N20" s="2" t="n">
-        <v>579163</v>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3990</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>3331</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>1286</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>7139</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -1878,145 +2640,225 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>643</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>460510</v>
+          <t>Está en el paro y ha trabajado antes</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>88282</t>
+        </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>60073</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>173368</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>656</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>516619</v>
+          <t>19,17%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>13,04%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>37,65%</t>
+        </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>94</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>76209</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="n">
-        <v>1299</v>
-      </c>
-      <c r="N21" s="2" t="n">
-        <v>977129</v>
+          <t>59201</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>96246</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>14,75%</t>
+        </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>164491</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>131922</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>239026</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>16,83%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>1855</v>
+          <t>Trabaja</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>257601</t>
+        </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>203246</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>281952</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>1487</v>
+          <t>55,94%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>44,13%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>61,23%</t>
+        </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>408</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>321561</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="N22" s="2" t="n">
-        <v>3342</v>
+          <t>297158</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>342798</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>62,24%</t>
+        </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>796</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>579163</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>528271</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>612419</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>59,27%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>54,06%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>62,68%</t>
         </is>
       </c>
     </row>
@@ -2024,141 +2866,229 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Incapacidad/invalidez permanente</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>1065</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>460510</t>
+        </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>460510</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>460510</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>1532</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>656</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>516619</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N23" s="2" t="n">
-        <v>2597</v>
+          <t>516619</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>516619</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1299</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>977129</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>977129</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>977129</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n"/>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Estudiante</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>2898</v>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>1094</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="N24" s="2" t="n">
-        <v>3991</v>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2166,70 +3096,112 @@
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Sus labores/Ama de casa</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>9519</v>
+          <t>Voluntariado social</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1855</t>
+        </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>7145</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>5839</v>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1487</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="N25" s="2" t="n">
-        <v>15358</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>3342</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>827</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>8029</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -2237,70 +3209,112 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Jubilado (trabajó anteriormente)</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>0</v>
+          <t>Incapacidad/invalidez permanente</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1065</t>
+        </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>3259</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>1498</v>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
+          <t>1532</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5499</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N26" s="2" t="n">
-        <v>1498</v>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>2597</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>6548</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -2308,70 +3322,112 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Busca primer empleo</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>0</v>
+          <t>Estudiante</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>2898</t>
+        </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
+          <t>734</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>6851</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>1094</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>6504</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>1236</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" s="2" t="n">
-        <v>1236</v>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>3991</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>1482</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>8657</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -2379,70 +3435,112 @@
       <c r="A28" s="1" t="n"/>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Está en el paro y ha trabajado antes</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>6792</v>
+          <t>Sus labores/Ama de casa/Trabajo doméstico no remunerado</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>9519</t>
+        </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>5659</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>15858</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>13466</v>
+          <t>6,36%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>3,78%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>10,6%</t>
+        </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="N28" s="2" t="n">
-        <v>20259</v>
+          <t>2570</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>12763</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>15358</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>9124</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>23487</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -2450,70 +3548,112 @@
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Trabaja</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>197</v>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>127421</v>
+          <t>Jubilado/a (trabajó anteriormente)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>205</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>157197</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>1498</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="n">
-        <v>402</v>
-      </c>
-      <c r="N29" s="2" t="n">
-        <v>284619</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>5695</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>1498</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>6134</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -2521,145 +3661,225 @@
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>230</v>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>149551</v>
+          <t>Busca primer empleo</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>238</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>183349</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="n">
-        <v>468</v>
-      </c>
-      <c r="N30" s="2" t="n">
-        <v>332900</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>7049</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>1236</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>7410</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A31" s="1" t="n"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>5875</v>
+          <t>Está en el paro y ha trabajado antes</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>6792</t>
+        </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>3652</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>12440</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>6591</v>
+          <t>4,54%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>8,32%</t>
+        </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>13466</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="N31" s="2" t="n">
-        <v>12466</v>
+          <t>7999</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>20744</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>7,34%</t>
+        </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>20259</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>13417</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>29429</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>6,09%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>4,03%</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -2667,70 +3887,112 @@
       <c r="A32" s="1" t="n"/>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Incapacidad/invalidez permanente</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>10839</v>
+          <t>Trabaja</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>127421</t>
+        </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>119444</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>133616</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>14826</v>
+          <t>85,2%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>79,87%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>89,34%</t>
+        </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>205</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>157197</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="N32" s="2" t="n">
-        <v>25665</v>
+          <t>146752</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>164503</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>85,74%</t>
+        </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>402</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>284619</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>273079</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>295108</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>85,5%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>82,03%</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>88,65%</t>
         </is>
       </c>
     </row>
@@ -2738,141 +4000,229 @@
       <c r="A33" s="1" t="n"/>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Estudiante</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>21474</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>149551</t>
+        </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>149551</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>149551</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>17605</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>238</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>183349</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="N33" s="2" t="n">
-        <v>39079</v>
+          <t>183349</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>183349</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>468</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>332900</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>332900</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>332900</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n"/>
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Sus labores/Ama de casa</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>139</v>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>101573</v>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>983</t>
+        </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>3088</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>134</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>105758</v>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="n">
-        <v>273</v>
-      </c>
-      <c r="N34" s="2" t="n">
-        <v>207331</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>983</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>3009</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
         </is>
       </c>
     </row>
@@ -2880,70 +4230,112 @@
       <c r="A35" s="1" t="n"/>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Jubilado (trabajó anteriormente)</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>11538</v>
+          <t>Voluntariado social</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>4892</t>
+        </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>12601</v>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>6591</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="N35" s="2" t="n">
-        <v>24139</v>
+          <t>3073</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>12382</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>11483</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>6781</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>18272</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -2951,70 +4343,112 @@
       <c r="A36" s="1" t="n"/>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Busca primer empleo</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>1866</v>
+          <t>Incapacidad/invalidez permanente</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10839</t>
+        </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>6476</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>18196</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>2700</v>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>14826</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="N36" s="2" t="n">
-        <v>4566</v>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>23687</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>25665</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>18530</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>35846</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -3022,70 +4456,112 @@
       <c r="A37" s="1" t="n"/>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Está en el paro y ha trabajado antes</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="D37" s="2" t="n">
-        <v>107113</v>
+          <t>Estudiante</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>21474</t>
+        </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>14223</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>29623</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>128</v>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>99043</v>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>4,46%</t>
+        </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>17605</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="n">
-        <v>238</v>
-      </c>
-      <c r="N37" s="2" t="n">
-        <v>206155</v>
+          <t>10526</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>26271</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>39079</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>29199</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>51459</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -3093,70 +4569,112 @@
       <c r="A38" s="1" t="n"/>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Trabaja</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>614</v>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>404460</v>
+          <t>Sus labores/Ama de casa/Trabajo doméstico no remunerado</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>101573</t>
+        </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>84079</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>119095</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>643</v>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>502848</v>
+          <t>15,28%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>12,65%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>17,92%</t>
+        </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>134</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>105758</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="n">
-        <v>1257</v>
-      </c>
-      <c r="N38" s="2" t="n">
-        <v>907308</v>
+          <t>89898</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>126105</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>13,88%</t>
+        </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>207331</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>183371</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>234829</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>14,53%</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>12,85%</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -3164,75 +4682,569 @@
       <c r="A39" s="1" t="n"/>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>942</v>
-      </c>
-      <c r="D39" s="2" t="n">
-        <v>664738</v>
+          <t>Jubilado/a (trabajó anteriormente)</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11538</t>
+        </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>18760</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>977</v>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>761972</v>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>12601</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="n">
-        <v>1919</v>
-      </c>
-      <c r="N39" s="2" t="n">
-        <v>1426710</v>
+          <t>7279</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>20055</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>24139</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>16407</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>33408</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="1" t="n"/>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Busca primer empleo</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>1866</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>528</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>5132</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>7805</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>4566</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>1728</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>9023</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n"/>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Está en el paro y ha trabajado antes</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>107113</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>77748</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>180355</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>16,11%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>11,7%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>27,13%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>99043</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>82035</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>120769</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>13,0%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10,77%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>15,85%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>206155</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>169145</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>284568</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>14,45%</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>11,86%</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>19,95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n"/>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Trabaja</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>404460</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>353199</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>432726</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>60,84%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>53,13%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>65,1%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>502848</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>475308</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>529194</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>65,99%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>62,38%</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>69,45%</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>1257</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>907308</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>846646</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>946512</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>63,59%</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>59,34%</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>66,34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n"/>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>664738</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>664738</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>664738</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>761972</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>761972</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>761972</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>1919</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>1426710</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>1426710</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>1426710</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -3240,14 +5252,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A13:A21"/>
-    <mergeCell ref="A22:A30"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="A4:A12"/>
-    <mergeCell ref="H1:L1"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="A24:A33"/>
+    <mergeCell ref="A34:A43"/>
+    <mergeCell ref="A4:A13"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A31:A39"/>
-    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="A14:A23"/>
+    <mergeCell ref="Q1:W1"/>
+    <mergeCell ref="C1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
